--- a/fixtures/style_gauntlet.xlsx
+++ b/fixtures/style_gauntlet.xlsx
@@ -1714,17 +1714,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>double underline (collapses to single-bit u)</t>
+          <t>double underline</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>double underline (collapses to single-bit u)</t>
+          <t>double underline</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>{"font": {"u": true}}</t>
+          <t>{"font": {"u": true, "u_double": true}}</t>
         </is>
       </c>
     </row>
